--- a/backend/data/financials_by_company/1101.HK.xlsx
+++ b/backend/data/financials_by_company/1101.HK.xlsx
@@ -662,134 +662,148 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-283700</v>
+        <v>-338000</v>
       </c>
       <c r="C2" t="n">
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-269850000</v>
+        <v>58600000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2837000</v>
+        <v>-3380000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2837000</v>
+        <v>-3380000</v>
       </c>
       <c r="G2" t="n">
-        <v>-526427000</v>
+        <v>-185066000</v>
       </c>
       <c r="H2" t="n">
-        <v>31417000</v>
+        <v>25699000</v>
       </c>
       <c r="I2" t="n">
-        <v>51129000</v>
+        <v>263698000</v>
       </c>
       <c r="J2" t="n">
-        <v>-272687000</v>
+        <v>55220000</v>
       </c>
       <c r="K2" t="n">
-        <v>-304104000</v>
+        <v>29521000</v>
       </c>
       <c r="L2" t="n">
-        <v>-219408000</v>
+        <v>-126710000</v>
       </c>
       <c r="M2" t="n">
-        <v>219408000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>200675000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>73965000</v>
+      </c>
       <c r="O2" t="n">
-        <v>-523873700</v>
+        <v>-182024000</v>
       </c>
       <c r="P2" t="n">
-        <v>-526427000</v>
+        <v>-185066000</v>
       </c>
       <c r="Q2" t="n">
-        <v>258402000</v>
+        <v>459121000</v>
       </c>
       <c r="R2" t="n">
-        <v>-11809000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>22094000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11776491507</v>
+      </c>
+      <c r="T2" t="n">
+        <v>11776491507</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="V2" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="W2" t="n">
-        <v>-526427000</v>
+        <v>-185066000</v>
       </c>
       <c r="X2" t="n">
-        <v>-526427000</v>
+        <v>-185066000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-526427000</v>
+        <v>-185066000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1307000</v>
+        <v>-7914000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-525120000</v>
+        <v>-177152000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-525120000</v>
+        <v>-177152000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1608000</v>
+        <v>5998000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-523512000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>-171154000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>272000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-2837000</v>
+        <v>-3380000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2837000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>3380000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-219408000</v>
+        <v>-126710000</v>
       </c>
       <c r="AK2" t="n">
-        <v>219408000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>200675000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>73965000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-175780000</v>
+        <v>-142347000</v>
       </c>
       <c r="AN2" t="n">
-        <v>207273000</v>
+        <v>195423000</v>
       </c>
       <c r="AO2" t="n">
         <v>163917000</v>
       </c>
       <c r="AP2" t="n">
-        <v>43414000</v>
+        <v>31506000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2600000</v>
+        <v>2654000</v>
       </c>
       <c r="AR2" t="n">
-        <v>40814000</v>
+        <v>28852000</v>
       </c>
       <c r="AS2" t="n">
-        <v>31493000</v>
+        <v>53076000</v>
       </c>
       <c r="AT2" t="n">
-        <v>51129000</v>
+        <v>263698000</v>
       </c>
       <c r="AU2" t="n">
-        <v>82622000</v>
+        <v>316774000</v>
       </c>
       <c r="AV2" t="n">
-        <v>82622000</v>
+        <v>316774000</v>
       </c>
     </row>
     <row r="3">
@@ -938,148 +952,134 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-338000</v>
+        <v>-283700</v>
       </c>
       <c r="C4" t="n">
         <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>58600000</v>
+        <v>-269850000</v>
       </c>
       <c r="E4" t="n">
-        <v>-3380000</v>
+        <v>-2837000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3380000</v>
+        <v>-2837000</v>
       </c>
       <c r="G4" t="n">
-        <v>-185066000</v>
+        <v>-526427000</v>
       </c>
       <c r="H4" t="n">
-        <v>25699000</v>
+        <v>31417000</v>
       </c>
       <c r="I4" t="n">
-        <v>263698000</v>
+        <v>51129000</v>
       </c>
       <c r="J4" t="n">
-        <v>55220000</v>
+        <v>-272687000</v>
       </c>
       <c r="K4" t="n">
-        <v>29521000</v>
+        <v>-304104000</v>
       </c>
       <c r="L4" t="n">
-        <v>-126710000</v>
+        <v>-219408000</v>
       </c>
       <c r="M4" t="n">
-        <v>200675000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>73965000</v>
-      </c>
+        <v>219408000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-182024000</v>
+        <v>-523873700</v>
       </c>
       <c r="P4" t="n">
-        <v>-185066000</v>
+        <v>-526427000</v>
       </c>
       <c r="Q4" t="n">
-        <v>459121000</v>
+        <v>258402000</v>
       </c>
       <c r="R4" t="n">
-        <v>22094000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>11776491507</v>
-      </c>
-      <c r="T4" t="n">
-        <v>11776491507</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.02</v>
-      </c>
+        <v>-11809000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="W4" t="n">
-        <v>-185066000</v>
+        <v>-526427000</v>
       </c>
       <c r="X4" t="n">
-        <v>-185066000</v>
+        <v>-526427000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-185066000</v>
+        <v>-526427000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-7914000</v>
+        <v>-1307000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-177152000</v>
+        <v>-525120000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-177152000</v>
+        <v>-525120000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5998000</v>
+        <v>1608000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-171154000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>272000</v>
-      </c>
+        <v>-523512000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-3380000</v>
+        <v>-2837000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3380000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>2837000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-126710000</v>
+        <v>-219408000</v>
       </c>
       <c r="AK4" t="n">
-        <v>200675000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>73965000</v>
-      </c>
+        <v>219408000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-142347000</v>
+        <v>-175780000</v>
       </c>
       <c r="AN4" t="n">
-        <v>195423000</v>
+        <v>207273000</v>
       </c>
       <c r="AO4" t="n">
         <v>163917000</v>
       </c>
       <c r="AP4" t="n">
-        <v>31506000</v>
+        <v>43414000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2654000</v>
+        <v>2600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>28852000</v>
+        <v>40814000</v>
       </c>
       <c r="AS4" t="n">
-        <v>53076000</v>
+        <v>31493000</v>
       </c>
       <c r="AT4" t="n">
-        <v>263698000</v>
+        <v>51129000</v>
       </c>
       <c r="AU4" t="n">
-        <v>316774000</v>
+        <v>82622000</v>
       </c>
       <c r="AV4" t="n">
-        <v>316774000</v>
+        <v>82622000</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>4770491507</v>
@@ -1404,44 +1404,46 @@
         <v>4770491507</v>
       </c>
       <c r="D2" t="n">
-        <v>3932573000</v>
+        <v>3556206000</v>
       </c>
       <c r="E2" t="n">
-        <v>3934716000</v>
+        <v>3580089000</v>
       </c>
       <c r="F2" t="n">
-        <v>-13218186000</v>
+        <v>-11998042000</v>
       </c>
       <c r="G2" t="n">
-        <v>-8380907000</v>
+        <v>-7589263000</v>
       </c>
       <c r="H2" t="n">
-        <v>-8108929000</v>
+        <v>-6988267000</v>
       </c>
       <c r="I2" t="n">
-        <v>-10118186000</v>
+        <v>-8898042000</v>
       </c>
       <c r="J2" t="n">
-        <v>-12315623000</v>
+        <v>-11169352000</v>
       </c>
       <c r="K2" t="n">
         <v>3100000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-6979809000</v>
+        <v>-5906678000</v>
       </c>
       <c r="M2" t="n">
-        <v>-9020675000</v>
+        <v>-7893114000</v>
       </c>
       <c r="N2" t="n">
-        <v>194948000</v>
+        <v>176238000</v>
       </c>
       <c r="O2" t="n">
-        <v>-9215623000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>-8069352000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12763000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-22847345000</v>
+        <v>-21650940000</v>
       </c>
       <c r="R2" t="n">
         <v>8374605000</v>
@@ -1456,121 +1458,121 @@
         <v>3100000000</v>
       </c>
       <c r="V2" t="n">
-        <v>10425805000</v>
+        <v>9274823000</v>
       </c>
       <c r="W2" t="n">
-        <v>2291416000</v>
+        <v>2222687000</v>
       </c>
       <c r="X2" t="n">
-        <v>55602000</v>
+        <v>60013000</v>
       </c>
       <c r="Y2" t="n">
-        <v>2235814000</v>
+        <v>2162674000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2235814000</v>
+        <v>2162674000</v>
       </c>
       <c r="AA2" t="n">
-        <v>8134389000</v>
+        <v>7052136000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1698902000</v>
+        <v>1417415000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1698902000</v>
+        <v>1417415000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1307470000</v>
+        <v>826833000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1032641000</v>
+        <v>554792000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17248000</v>
+        <v>15716000</v>
       </c>
       <c r="AG2" t="n">
-        <v>257581000</v>
+        <v>256325000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1405130000</v>
+        <v>1381709000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1379670000</v>
+        <v>1317840000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17083000</v>
+        <v>13143000</v>
       </c>
       <c r="AK2" t="n">
-        <v>902563000</v>
+        <v>828690000</v>
       </c>
       <c r="AL2" t="n">
-        <v>869216000</v>
+        <v>795343000</v>
       </c>
       <c r="AM2" t="n">
         <v>33347000</v>
       </c>
       <c r="AN2" t="n">
-        <v>460024000</v>
+        <v>476007000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-397165000</v>
+        <v>-437019000</v>
       </c>
       <c r="AP2" t="n">
-        <v>848615000</v>
+        <v>910281000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30585000</v>
+        <v>132094000</v>
       </c>
       <c r="AR2" t="n">
-        <v>72303000</v>
+        <v>63451000</v>
       </c>
       <c r="AS2" t="n">
-        <v>52955000</v>
+        <v>52418000</v>
       </c>
       <c r="AT2" t="n">
         <v>115818000</v>
       </c>
       <c r="AU2" t="n">
-        <v>576954000</v>
+        <v>546500000</v>
       </c>
       <c r="AV2" t="n">
-        <v>25460000</v>
+        <v>63869000</v>
       </c>
       <c r="AW2" t="n">
-        <v>981000</v>
+        <v>9840000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2975000</v>
+        <v>4305000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2349000</v>
+        <v>3381000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>626000</v>
+        <v>924000</v>
       </c>
       <c r="BA2" t="n">
-        <v>4191000</v>
+        <v>6767000</v>
       </c>
       <c r="BB2" t="n">
-        <v>7562000</v>
+        <v>7150000</v>
       </c>
       <c r="BC2" t="n">
-        <v>7608000</v>
+        <v>11924000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-5466000</v>
+        <v>-850000</v>
       </c>
       <c r="BE2" t="n">
-        <v>13074000</v>
+        <v>12774000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2143000</v>
+        <v>23883000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2143000</v>
+        <v>23883000</v>
       </c>
       <c r="BH2" t="n">
-        <v>2143000</v>
+        <v>23883000</v>
       </c>
     </row>
     <row r="3">
@@ -1755,7 +1757,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>4770491507</v>
@@ -1764,46 +1766,44 @@
         <v>4770491507</v>
       </c>
       <c r="D4" t="n">
-        <v>3556206000</v>
+        <v>3932573000</v>
       </c>
       <c r="E4" t="n">
-        <v>3580089000</v>
+        <v>3934716000</v>
       </c>
       <c r="F4" t="n">
-        <v>-11998042000</v>
+        <v>-13218186000</v>
       </c>
       <c r="G4" t="n">
-        <v>-7589263000</v>
+        <v>-8380907000</v>
       </c>
       <c r="H4" t="n">
-        <v>-6988267000</v>
+        <v>-8108929000</v>
       </c>
       <c r="I4" t="n">
-        <v>-8898042000</v>
+        <v>-10118186000</v>
       </c>
       <c r="J4" t="n">
-        <v>-11169352000</v>
+        <v>-12315623000</v>
       </c>
       <c r="K4" t="n">
         <v>3100000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-5906678000</v>
+        <v>-6979809000</v>
       </c>
       <c r="M4" t="n">
-        <v>-7893114000</v>
+        <v>-9020675000</v>
       </c>
       <c r="N4" t="n">
-        <v>176238000</v>
+        <v>194948000</v>
       </c>
       <c r="O4" t="n">
-        <v>-8069352000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12763000</v>
-      </c>
+        <v>-9215623000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-21650940000</v>
+        <v>-22847345000</v>
       </c>
       <c r="R4" t="n">
         <v>8374605000</v>
@@ -1818,121 +1818,121 @@
         <v>3100000000</v>
       </c>
       <c r="V4" t="n">
-        <v>9274823000</v>
+        <v>10425805000</v>
       </c>
       <c r="W4" t="n">
-        <v>2222687000</v>
+        <v>2291416000</v>
       </c>
       <c r="X4" t="n">
-        <v>60013000</v>
+        <v>55602000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2162674000</v>
+        <v>2235814000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2162674000</v>
+        <v>2235814000</v>
       </c>
       <c r="AA4" t="n">
-        <v>7052136000</v>
+        <v>8134389000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1417415000</v>
+        <v>1698902000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1417415000</v>
+        <v>1698902000</v>
       </c>
       <c r="AD4" t="n">
-        <v>826833000</v>
+        <v>1307470000</v>
       </c>
       <c r="AE4" t="n">
-        <v>554792000</v>
+        <v>1032641000</v>
       </c>
       <c r="AF4" t="n">
-        <v>15716000</v>
+        <v>17248000</v>
       </c>
       <c r="AG4" t="n">
-        <v>256325000</v>
+        <v>257581000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1381709000</v>
+        <v>1405130000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1317840000</v>
+        <v>1379670000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13143000</v>
+        <v>17083000</v>
       </c>
       <c r="AK4" t="n">
-        <v>828690000</v>
+        <v>902563000</v>
       </c>
       <c r="AL4" t="n">
-        <v>795343000</v>
+        <v>869216000</v>
       </c>
       <c r="AM4" t="n">
         <v>33347000</v>
       </c>
       <c r="AN4" t="n">
-        <v>476007000</v>
+        <v>460024000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-437019000</v>
+        <v>-397165000</v>
       </c>
       <c r="AP4" t="n">
-        <v>910281000</v>
+        <v>848615000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>132094000</v>
+        <v>30585000</v>
       </c>
       <c r="AR4" t="n">
-        <v>63451000</v>
+        <v>72303000</v>
       </c>
       <c r="AS4" t="n">
-        <v>52418000</v>
+        <v>52955000</v>
       </c>
       <c r="AT4" t="n">
         <v>115818000</v>
       </c>
       <c r="AU4" t="n">
-        <v>546500000</v>
+        <v>576954000</v>
       </c>
       <c r="AV4" t="n">
-        <v>63869000</v>
+        <v>25460000</v>
       </c>
       <c r="AW4" t="n">
-        <v>9840000</v>
+        <v>981000</v>
       </c>
       <c r="AX4" t="n">
-        <v>4305000</v>
+        <v>2975000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3381000</v>
+        <v>2349000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>924000</v>
+        <v>626000</v>
       </c>
       <c r="BA4" t="n">
-        <v>6767000</v>
+        <v>4191000</v>
       </c>
       <c r="BB4" t="n">
-        <v>7150000</v>
+        <v>7562000</v>
       </c>
       <c r="BC4" t="n">
-        <v>11924000</v>
+        <v>7608000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-850000</v>
+        <v>-5466000</v>
       </c>
       <c r="BE4" t="n">
-        <v>12774000</v>
+        <v>13074000</v>
       </c>
       <c r="BF4" t="n">
-        <v>23883000</v>
+        <v>2143000</v>
       </c>
       <c r="BG4" t="n">
-        <v>23883000</v>
+        <v>2143000</v>
       </c>
       <c r="BH4" t="n">
-        <v>23883000</v>
+        <v>2143000</v>
       </c>
     </row>
   </sheetData>
@@ -2128,108 +2128,110 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1030000</v>
+        <v>17536000</v>
       </c>
       <c r="C2" t="n">
-        <v>-13129000</v>
+        <v>-50758000</v>
       </c>
       <c r="D2" t="n">
-        <v>1439000</v>
+        <v>40806000</v>
       </c>
       <c r="E2" t="n">
-        <v>-8067000</v>
+        <v>-10823000</v>
       </c>
       <c r="F2" t="n">
-        <v>2143000</v>
+        <v>23883000</v>
       </c>
       <c r="G2" t="n">
-        <v>14583000</v>
+        <v>16064000</v>
       </c>
       <c r="H2" t="n">
-        <v>280000</v>
+        <v>-203000</v>
       </c>
       <c r="I2" t="n">
-        <v>-12720000</v>
+        <v>8022000</v>
       </c>
       <c r="J2" t="n">
-        <v>-11690000</v>
+        <v>-9952000</v>
       </c>
       <c r="K2" t="n">
-        <v>-11690000</v>
+        <v>-9952000</v>
       </c>
       <c r="L2" t="n">
-        <v>-11690000</v>
+        <v>-9952000</v>
       </c>
       <c r="M2" t="n">
-        <v>-13129000</v>
+        <v>-50758000</v>
       </c>
       <c r="N2" t="n">
-        <v>1439000</v>
+        <v>40806000</v>
       </c>
       <c r="O2" t="n">
-        <v>-8067000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>-10385000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>159000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>159000</v>
+      </c>
       <c r="R2" t="n">
-        <v>-8067000</v>
+        <v>-10544000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>279000</v>
       </c>
       <c r="T2" t="n">
-        <v>-8067000</v>
+        <v>-10823000</v>
       </c>
       <c r="U2" t="n">
-        <v>7037000</v>
+        <v>28359000</v>
       </c>
       <c r="V2" t="n">
-        <v>-3813000</v>
+        <v>-3783000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-1866000</v>
       </c>
       <c r="X2" t="n">
-        <v>-12191000</v>
+        <v>-12433000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-16495000</v>
+        <v>-51735000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2006000</v>
+        <v>-1721000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2298000</v>
+        <v>41023000</v>
       </c>
       <c r="AB2" t="n">
-        <v>219408000</v>
+        <v>126710000</v>
       </c>
       <c r="AC2" t="n">
-        <v>164294000</v>
+        <v>164794000</v>
       </c>
       <c r="AD2" t="n">
-        <v>31417000</v>
+        <v>25699000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1278000</v>
+        <v>1489000</v>
       </c>
       <c r="AF2" t="n">
-        <v>30139000</v>
+        <v>24210000</v>
       </c>
       <c r="AG2" t="n">
-        <v>125487000</v>
+        <v>-101011000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1243000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1594000</v>
-      </c>
+        <v>3380000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-523512000</v>
+        <v>-171154000</v>
       </c>
     </row>
     <row r="3">
@@ -2344,110 +2346,108 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>17536000</v>
+        <v>-1030000</v>
       </c>
       <c r="C4" t="n">
-        <v>-50758000</v>
+        <v>-13129000</v>
       </c>
       <c r="D4" t="n">
-        <v>40806000</v>
+        <v>1439000</v>
       </c>
       <c r="E4" t="n">
-        <v>-10823000</v>
+        <v>-8067000</v>
       </c>
       <c r="F4" t="n">
-        <v>23883000</v>
+        <v>2143000</v>
       </c>
       <c r="G4" t="n">
-        <v>16064000</v>
+        <v>14583000</v>
       </c>
       <c r="H4" t="n">
-        <v>-203000</v>
+        <v>280000</v>
       </c>
       <c r="I4" t="n">
-        <v>8022000</v>
+        <v>-12720000</v>
       </c>
       <c r="J4" t="n">
-        <v>-9952000</v>
+        <v>-11690000</v>
       </c>
       <c r="K4" t="n">
-        <v>-9952000</v>
+        <v>-11690000</v>
       </c>
       <c r="L4" t="n">
-        <v>-9952000</v>
+        <v>-11690000</v>
       </c>
       <c r="M4" t="n">
-        <v>-50758000</v>
+        <v>-13129000</v>
       </c>
       <c r="N4" t="n">
-        <v>40806000</v>
+        <v>1439000</v>
       </c>
       <c r="O4" t="n">
-        <v>-10385000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>159000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>159000</v>
-      </c>
+        <v>-8067000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-10544000</v>
+        <v>-8067000</v>
       </c>
       <c r="S4" t="n">
-        <v>279000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-10823000</v>
+        <v>-8067000</v>
       </c>
       <c r="U4" t="n">
-        <v>28359000</v>
+        <v>7037000</v>
       </c>
       <c r="V4" t="n">
-        <v>-3783000</v>
+        <v>-3813000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1866000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-12433000</v>
+        <v>-12191000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-51735000</v>
+        <v>-16495000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1721000</v>
+        <v>2006000</v>
       </c>
       <c r="AA4" t="n">
-        <v>41023000</v>
+        <v>2298000</v>
       </c>
       <c r="AB4" t="n">
-        <v>126710000</v>
+        <v>219408000</v>
       </c>
       <c r="AC4" t="n">
-        <v>164794000</v>
+        <v>164294000</v>
       </c>
       <c r="AD4" t="n">
-        <v>25699000</v>
+        <v>31417000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1489000</v>
+        <v>1278000</v>
       </c>
       <c r="AF4" t="n">
-        <v>24210000</v>
+        <v>30139000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-101011000</v>
+        <v>125487000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3380000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>1243000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1594000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-171154000</v>
+        <v>-523512000</v>
       </c>
     </row>
   </sheetData>
@@ -2972,192 +2972,192 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jianmin  Niu', 'age': 57, 'title': 'Executive Chairman', 'yearBorn': 1968, 'fiscalYear': 2023, 'totalPay': 1859298, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Hong', 'age': 54, 'title': 'CEO, COO &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2023, 'totalPay': 988150, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wen Hua  Zhu', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2023, 'totalPay': 1443418, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Fai  Leung Acca, C.P.A., Cpa Australia, Hkicpa', 'age': 60, 'title': 'Company Secretary', 'yearBorn': 1965, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jianmin  Niu', 'age': 57, 'title': 'Executive Chairman', 'yearBorn': 1968, 'fiscalYear': 2023, 'totalPay': 1857817, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Hong', 'age': 54, 'title': 'CEO, COO &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2023, 'totalPay': 987363, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wen Hua  Zhu', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2023, 'totalPay': 1442268, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Fai  Leung Acca, C.P.A., Cpa Australia, Hkicpa', 'age': 60, 'title': 'Company Secretary', 'yearBorn': 1965, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.582</v>
+        <v>0.587</v>
       </c>
       <c r="AF2" t="n">
         <v>477700</v>
@@ -3382,7 +3382,7 @@
         <v>4770491507</v>
       </c>
       <c r="BI2" t="n">
-        <v>-3.0702338</v>
+        <v>-3.0686047</v>
       </c>
       <c r="BJ2" t="n">
         <v>1703980800</v>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.134985</v>
@@ -3524,92 +3524,80 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>HUARONG ENERGY</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CZ2" t="n">
-        <v>1724924965</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1724924965</v>
-      </c>
-      <c r="DB2" t="b">
+      <c r="CX2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-0.0030000005</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.02 - 0.024</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
         <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>0.02 - 0.024</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.0040000007</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.16666669</v>
+      </c>
+      <c r="DH2" t="n">
         <v>0</v>
       </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.006514162</v>
-      </c>
       <c r="DI2" t="n">
-        <v>15</v>
+        <v>1724924965</v>
       </c>
       <c r="DJ2" t="n">
-        <v>15</v>
+        <v>1724924965</v>
       </c>
       <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>China Huarong Energy Company Limited</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="DL2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>1743407903</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>finmb_115210600</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.00651762</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
       </c>
       <c r="DS2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
       </c>
       <c r="DU2" t="b">
         <v>0</v>
@@ -3620,47 +3608,59 @@
       <c r="DW2" t="n">
         <v>1290130200000</v>
       </c>
-      <c r="DX2" t="n">
-        <v>-0.0030000005</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>0.02 - 0.024</t>
-        </is>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>China Huarong Energy Company Limited</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-13.043481</v>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>0.02 - 0.024</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.0040000007</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.16666669</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0</v>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>finmb_115210600</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EH2" t="n">
-        <v>-13.043481</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.02</v>
+        <v>1743407903</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>HUARONG ENERGY</t>
+        </is>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
